--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126928112</v>
       </c>
       <c r="B3" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B10" t="n">
-        <v>97242</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R10" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>97317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,39 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R11" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
         <v>126925986</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126926421</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>126928956</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126927572</v>
       </c>
       <c r="B15" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126928112</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>126928354</v>
       </c>
       <c r="B11" t="n">
-        <v>97317</v>
+        <v>97323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126925986</v>
       </c>
       <c r="B12" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126926421</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>126928956</v>
       </c>
       <c r="B14" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126927572</v>
       </c>
       <c r="B15" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R6" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R7" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126925986</v>
+        <v>126926421</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585313</v>
+        <v>585431</v>
       </c>
       <c r="R12" t="n">
-        <v>6938628</v>
+        <v>6938655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126926421</v>
+        <v>126925986</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585431</v>
+        <v>585313</v>
       </c>
       <c r="R13" t="n">
-        <v>6938655</v>
+        <v>6938628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126928112</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R6" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1191,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R7" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>97324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1497,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R10" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B11" t="n">
-        <v>97323</v>
+        <v>58027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1594,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R11" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126926421</v>
+        <v>126925986</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585431</v>
+        <v>585313</v>
       </c>
       <c r="R12" t="n">
-        <v>6938655</v>
+        <v>6938628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126925986</v>
+        <v>126926421</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585313</v>
+        <v>585431</v>
       </c>
       <c r="R13" t="n">
-        <v>6938628</v>
+        <v>6938655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
         <v>126928956</v>
       </c>
       <c r="B14" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126927572</v>
       </c>
       <c r="B15" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B10" t="n">
-        <v>97324</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R10" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>97324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,39 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R11" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R6" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R7" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R6" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1191,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R7" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>97324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1497,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R10" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B11" t="n">
-        <v>97324</v>
+        <v>58027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1594,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R11" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126926105</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126928112</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126925641</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126926399</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126925809</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>126928786</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126927840</v>
       </c>
       <c r="B9" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B10" t="n">
-        <v>97324</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R10" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>97328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,39 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R11" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126925986</v>
+        <v>126926421</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585313</v>
+        <v>585431</v>
       </c>
       <c r="R12" t="n">
-        <v>6938628</v>
+        <v>6938655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126926421</v>
+        <v>126925986</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585431</v>
+        <v>585313</v>
       </c>
       <c r="R13" t="n">
-        <v>6938655</v>
+        <v>6938628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
         <v>126928956</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126927572</v>
       </c>
       <c r="B15" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R6" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R7" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R6" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1191,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R7" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126926421</v>
+        <v>126925986</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585431</v>
+        <v>585313</v>
       </c>
       <c r="R12" t="n">
-        <v>6938655</v>
+        <v>6938628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126925986</v>
+        <v>126926421</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585313</v>
+        <v>585431</v>
       </c>
       <c r="R13" t="n">
-        <v>6938628</v>
+        <v>6938655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126926105</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126928112</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126925641</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126926399</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126925809</v>
+        <v>126926179</v>
       </c>
       <c r="B6" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585241</v>
+        <v>585374</v>
       </c>
       <c r="R6" t="n">
-        <v>6938648</v>
+        <v>6938611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126926179</v>
+        <v>126925809</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1191,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585374</v>
+        <v>585241</v>
       </c>
       <c r="R7" t="n">
-        <v>6938611</v>
+        <v>6938648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
         <v>126928786</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126927840</v>
       </c>
       <c r="B9" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>97330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1497,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R10" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B11" t="n">
-        <v>97328</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1594,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R11" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
         <v>126925986</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126926421</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>126928956</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126927572</v>
       </c>
       <c r="B15" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25042-2025 artfynd.xlsx
+++ b/artfynd/A 25042-2025 artfynd.xlsx
@@ -1486,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126928354</v>
+        <v>126927351</v>
       </c>
       <c r="B10" t="n">
-        <v>97330</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585212</v>
+        <v>585271</v>
       </c>
       <c r="R10" t="n">
-        <v>6938677</v>
+        <v>6938703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126927351</v>
+        <v>126928354</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>97330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,39 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rallbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585271</v>
+        <v>585212</v>
       </c>
       <c r="R11" t="n">
-        <v>6938703</v>
+        <v>6938677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
